--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/SOUTH_DAKOTA_2018.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/SOUTH_DAKOTA_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D197"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Metapa</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Teopisca</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Chínipas</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -688,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C24">
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -745,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -758,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Sabinas</t>
@@ -771,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Saltillo</t>
@@ -784,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -797,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -810,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -841,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -854,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -869,7 +1009,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -885,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -898,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -911,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -924,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -937,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -950,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Súchil</t>
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1022,12 +1207,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C48">
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C49">
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1064,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Timilpan</t>
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1090,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1121,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1134,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>León</t>
@@ -1147,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Manuel Doblado</t>
@@ -1160,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -1173,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C59">
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -1212,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C62">
@@ -1225,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C63">
@@ -1238,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1251,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1271,7 +1536,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C66">
@@ -1282,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1295,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C68">
@@ -1308,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C69">
@@ -1321,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1334,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C71">
@@ -1347,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1360,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -1373,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C74">
@@ -1386,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -1399,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -1412,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Pilcaya</t>
@@ -1425,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -1438,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -1451,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C80">
@@ -1464,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1477,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1508,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C84">
@@ -1521,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Eloxochitlán</t>
@@ -1534,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C86">
@@ -1547,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C87">
@@ -1560,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1591,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -1604,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1617,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1630,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -1643,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Mezquitic</t>
@@ -1656,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Poncitlán</t>
@@ -1669,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -1682,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C97">
@@ -1695,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C98">
@@ -1708,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -1721,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Unión de San Antonio</t>
+          <t>Unión De San Antonio</t>
         </is>
       </c>
       <c r="C100">
@@ -1734,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C101">
@@ -1747,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1760,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -1773,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1804,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -1817,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -1830,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Coahuayana</t>
@@ -1843,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Coalcomán de Vázquez Pallares</t>
+          <t>Coalcomán De Vázquez Pallares</t>
         </is>
       </c>
       <c r="C109">
@@ -1856,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Jungapeo</t>
@@ -1869,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1882,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1895,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -1908,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Tarímbaro</t>
@@ -1921,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -1934,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -1947,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -1960,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1973,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2004,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -2017,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2048,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -2061,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>San Pedro Lagunillas</t>
@@ -2074,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2087,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2118,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -2131,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -2144,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2164,7 +2724,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C132">
@@ -2175,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Magdalena Tequisistlán</t>
@@ -2188,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>San Juan Lachao</t>
@@ -2201,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -2214,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>San Mateo del Mar</t>
+          <t>San Mateo Del Mar</t>
         </is>
       </c>
       <c r="C136">
@@ -2227,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>San Vicente Coatlán</t>
@@ -2240,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -2253,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -2266,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -2279,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Santo Domingo Tonalá</t>
@@ -2292,9 +2897,14 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Villa de Etla</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C142">
@@ -2305,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Zapotitlán del Río</t>
+          <t>Zapotitlán Del Río</t>
         </is>
       </c>
       <c r="C143">
@@ -2318,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2349,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Cuautlancingo</t>
@@ -2362,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -2375,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>San José Miahuatlán</t>
@@ -2388,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -2401,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -2414,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -2427,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -2440,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2471,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2502,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -2515,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -2528,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C159">
@@ -2541,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -2554,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C161">
@@ -2567,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C162">
@@ -2580,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2611,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -2624,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2655,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2686,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -2699,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2730,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C173">
@@ -2743,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C174">
@@ -2756,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -2769,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -2782,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C177">
@@ -2795,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C178">
@@ -2808,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2821,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Tlapacoyan</t>
@@ -2834,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2847,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2878,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -2891,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -2904,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -2917,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -2930,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Susticacán</t>
@@ -2943,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -2956,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2979,41 +3789,6 @@
       </c>
       <c r="D191">
         <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
